--- a/src/src/main/webapp/portal/pm/pmOrderListRemote_export.xlsx
+++ b/src/src/main/webapp/portal/pm/pmOrderListRemote_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="7">
   <si>
     <t>资产名称</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t>状态</t>
+  </si>
+  <si>
+    <t>保养计划时间</t>
   </si>
 </sst>
 </file>
@@ -269,13 +272,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -374,10 +371,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Cambria"/>
-            <a:ea typeface="Cambria"/>
-            <a:cs typeface="Cambria"/>
-            <a:sym typeface="Cambria"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -632,13 +629,7 @@
           <a:prstDash val="solid"/>
           <a:round/>
         </a:ln>
-        <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
-            <a:srgbClr val="000000">
-              <a:alpha val="38000"/>
-            </a:srgbClr>
-          </a:outerShdw>
-        </a:effectLst>
+        <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
@@ -951,10 +942,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Cambria"/>
-            <a:ea typeface="Cambria"/>
-            <a:cs typeface="Cambria"/>
-            <a:sym typeface="Cambria"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1205,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="24.3516" style="1" customWidth="1"/>
@@ -1213,8 +1204,8 @@
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.1719" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.35156" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="256" width="8.85156" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" style="1" customWidth="1"/>
+    <col min="8" max="256" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="19" customHeight="1">
@@ -1236,6 +1227,9 @@
       <c r="F1" t="s" s="2">
         <v>5</v>
       </c>
+      <c r="G1" t="s" s="2">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
